--- a/research/traditional_assets/database/data/australia/australia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111</v>
+        <v>0.2175</v>
       </c>
       <c r="E2">
-        <v>0.142</v>
+        <v>0.196</v>
       </c>
       <c r="F2">
-        <v>0.064</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="G2">
-        <v>0.3082535715551774</v>
+        <v>0.3109295174450982</v>
       </c>
       <c r="H2">
-        <v>0.3082535715551774</v>
+        <v>0.3109295174450982</v>
       </c>
       <c r="I2">
-        <v>0.2595411705574139</v>
+        <v>0.5796859584597266</v>
       </c>
       <c r="J2">
-        <v>0.21014742183372</v>
+        <v>0.4563413092709121</v>
       </c>
       <c r="K2">
-        <v>189.423</v>
+        <v>192.489</v>
       </c>
       <c r="L2">
-        <v>0.1678746144847389</v>
+        <v>0.1553545918985013</v>
       </c>
       <c r="M2">
-        <v>106.02</v>
+        <v>131.88</v>
       </c>
       <c r="N2">
-        <v>0.01695668863156548</v>
+        <v>0.01991453120517041</v>
       </c>
       <c r="O2">
-        <v>0.5596997196750131</v>
+        <v>0.6851300593800165</v>
       </c>
       <c r="P2">
-        <v>101.6</v>
+        <v>127.4</v>
       </c>
       <c r="Q2">
-        <v>0.01624976009212463</v>
+        <v>0.01923802908355103</v>
       </c>
       <c r="R2">
-        <v>0.5363657000469848</v>
+        <v>0.6618560021611624</v>
       </c>
       <c r="S2">
-        <v>4.420000000000002</v>
+        <v>4.480000000000004</v>
       </c>
       <c r="T2">
-        <v>0.04169024712318432</v>
+        <v>0.0339702760084926</v>
       </c>
       <c r="U2">
-        <v>267.7</v>
+        <v>445.302</v>
       </c>
       <c r="V2">
-        <v>0.04281555882541104</v>
+        <v>0.06724280083958746</v>
       </c>
       <c r="W2">
-        <v>0.1799560797433473</v>
+        <v>0.1456230786519276</v>
       </c>
       <c r="X2">
-        <v>0.04675612876671753</v>
+        <v>0.07864605362478236</v>
       </c>
       <c r="Y2">
-        <v>0.1331999509766298</v>
+        <v>0.0669770250271452</v>
       </c>
       <c r="Z2">
-        <v>1.413843889932277</v>
+        <v>1.004224664835961</v>
       </c>
       <c r="AA2">
-        <v>0.2743655110564651</v>
+        <v>0.3241756232152957</v>
       </c>
       <c r="AB2">
-        <v>0.04296418930680108</v>
+        <v>0.07291532884039992</v>
       </c>
       <c r="AC2">
-        <v>0.2314877030398524</v>
+        <v>0.2503927532758544</v>
       </c>
       <c r="AD2">
-        <v>923.24</v>
+        <v>843.271</v>
       </c>
       <c r="AE2">
-        <v>0.9856239491817239</v>
+        <v>464.9335344482246</v>
       </c>
       <c r="AF2">
-        <v>924.2256239491817</v>
+        <v>1308.204534448225</v>
       </c>
       <c r="AG2">
-        <v>656.5256239491816</v>
+        <v>862.9025344482246</v>
       </c>
       <c r="AH2">
-        <v>0.1287827556261177</v>
+        <v>0.1649585507158713</v>
       </c>
       <c r="AI2">
-        <v>0.3578705547290864</v>
+        <v>0.3705568691602543</v>
       </c>
       <c r="AJ2">
-        <v>0.09502571885755919</v>
+        <v>0.1152811203807772</v>
       </c>
       <c r="AK2">
-        <v>0.2836123543014681</v>
+        <v>0.2797025109824711</v>
       </c>
       <c r="AL2">
-        <v>24.417</v>
+        <v>23.674</v>
       </c>
       <c r="AM2">
-        <v>23.367</v>
+        <v>23.128</v>
       </c>
       <c r="AN2">
-        <v>2.647882961301628</v>
+        <v>0.9669973430453036</v>
       </c>
       <c r="AO2">
-        <v>11.96719498709915</v>
+        <v>13.70427473177325</v>
       </c>
       <c r="AP2">
-        <v>1.882937278836444</v>
+        <v>0.9895092539865498</v>
       </c>
       <c r="AQ2">
-        <v>12.50494286814739</v>
+        <v>14.02780179868558</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08500000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="E3">
-        <v>0.11</v>
+        <v>0.196</v>
       </c>
       <c r="F3">
-        <v>0.064</v>
+        <v>0.101</v>
       </c>
       <c r="G3">
-        <v>0.2973075464543042</v>
+        <v>0.2750292169848071</v>
       </c>
       <c r="H3">
-        <v>0.2973075464543042</v>
+        <v>0.2750292169848071</v>
       </c>
       <c r="I3">
-        <v>0.2637575851731652</v>
+        <v>1.777613140281866</v>
       </c>
       <c r="J3">
-        <v>0.2158955690647188</v>
+        <v>1.452491497047416</v>
       </c>
       <c r="K3">
-        <v>52.9</v>
+        <v>55.7</v>
       </c>
       <c r="L3">
-        <v>0.2006067500948047</v>
+        <v>0.2169848071679003</v>
       </c>
       <c r="M3">
-        <v>35</v>
+        <v>28.7</v>
       </c>
       <c r="N3">
-        <v>0.02509500250950025</v>
+        <v>0.01846015308419631</v>
       </c>
       <c r="O3">
-        <v>0.6616257088846881</v>
+        <v>0.5152603231597845</v>
       </c>
       <c r="P3">
-        <v>35</v>
+        <v>28.7</v>
       </c>
       <c r="Q3">
-        <v>0.02509500250950025</v>
+        <v>0.01846015308419631</v>
       </c>
       <c r="R3">
-        <v>0.6616257088846881</v>
+        <v>0.5152603231597845</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>57.4</v>
+        <v>178.7</v>
       </c>
       <c r="V3">
-        <v>0.04115580411558041</v>
+        <v>0.1149417894127484</v>
       </c>
       <c r="W3">
-        <v>0.1784750337381917</v>
+        <v>0.155196433546949</v>
       </c>
       <c r="X3">
-        <v>0.04640431705240005</v>
+        <v>0.08340977515835937</v>
       </c>
       <c r="Y3">
-        <v>0.1320707166857916</v>
+        <v>0.07178665838858966</v>
       </c>
       <c r="Z3">
-        <v>1.372110954926204</v>
+        <v>0.4056358995321256</v>
       </c>
       <c r="AA3">
-        <v>0.2962326754337274</v>
+        <v>0.5891826949675923</v>
       </c>
       <c r="AB3">
-        <v>0.04297670115044403</v>
+        <v>0.07086761395294827</v>
       </c>
       <c r="AC3">
-        <v>0.2532559742832833</v>
+        <v>0.5183150810146441</v>
       </c>
       <c r="AD3">
-        <v>178.5</v>
+        <v>51.5</v>
       </c>
       <c r="AE3">
-        <v>0.9856239491817239</v>
+        <v>464.9335344482246</v>
       </c>
       <c r="AF3">
-        <v>179.4856239491817</v>
+        <v>516.4335344482247</v>
       </c>
       <c r="AG3">
-        <v>122.0856239491817</v>
+        <v>337.7335344482247</v>
       </c>
       <c r="AH3">
-        <v>0.114018080980122</v>
+        <v>0.2493482558505378</v>
       </c>
       <c r="AI3">
-        <v>0.285766171211879</v>
+        <v>0.4289908194698457</v>
       </c>
       <c r="AJ3">
-        <v>0.08048970271178682</v>
+        <v>0.1784652027669217</v>
       </c>
       <c r="AK3">
-        <v>0.2139279821074539</v>
+        <v>0.3294532108248793</v>
       </c>
       <c r="AL3">
-        <v>5.71</v>
+        <v>4.65</v>
       </c>
       <c r="AM3">
-        <v>5.71</v>
+        <v>4.65</v>
       </c>
       <c r="AN3">
-        <v>2.252365930599369</v>
+        <v>0.09239325439540726</v>
       </c>
       <c r="AO3">
-        <v>12.06654991243433</v>
+        <v>13.44086021505376</v>
       </c>
       <c r="AP3">
-        <v>1.540512605036993</v>
+        <v>0.6059087449734925</v>
       </c>
       <c r="AQ3">
-        <v>12.06654991243433</v>
+        <v>13.44086021505376</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PSC Insurance Group Limited (ASX:PSI)</t>
+          <t>Ensurance Limited (ASX:ENA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,121 +862,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.253</v>
-      </c>
-      <c r="E4">
-        <v>0.323</v>
+        <v>0.486</v>
       </c>
       <c r="G4">
-        <v>0.3013698630136986</v>
+        <v>0.1095427435387674</v>
       </c>
       <c r="H4">
-        <v>0.3013698630136986</v>
+        <v>0.1095427435387674</v>
       </c>
       <c r="I4">
-        <v>0.2472276581865623</v>
+        <v>0.1063618290258449</v>
       </c>
       <c r="J4">
-        <v>0.1729459535479392</v>
+        <v>0.1063618290258449</v>
       </c>
       <c r="K4">
-        <v>30.3</v>
+        <v>0.189</v>
       </c>
       <c r="L4">
-        <v>0.1976516634050881</v>
+        <v>0.03757455268389662</v>
       </c>
       <c r="M4">
-        <v>20.6</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.01828186013489528</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6798679867986799</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>20.6</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.01828186013489528</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.6798679867986799</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>35.9</v>
+        <v>0.702</v>
       </c>
       <c r="V4">
-        <v>0.03186013489527866</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="W4">
-        <v>0.181437125748503</v>
+        <v>1.3125</v>
       </c>
       <c r="X4">
-        <v>0.04649156816829444</v>
+        <v>0.07511379131035709</v>
       </c>
       <c r="Y4">
-        <v>0.1349455575802085</v>
+        <v>1.237386208689643</v>
       </c>
       <c r="Z4">
-        <v>1.66088840736728</v>
+        <v>3.175505050505051</v>
       </c>
       <c r="AA4">
-        <v>0.2872439293488524</v>
+        <v>0.3377525252525252</v>
       </c>
       <c r="AB4">
-        <v>0.04295167746315814</v>
+        <v>0.07495383383022734</v>
       </c>
       <c r="AC4">
-        <v>0.2442922518856943</v>
+        <v>0.2627986914222979</v>
       </c>
       <c r="AD4">
-        <v>149.9</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>149.9</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AG4">
-        <v>114</v>
+        <v>-0.631</v>
       </c>
       <c r="AH4">
-        <v>0.1174120780136289</v>
+        <v>0.004711034436998208</v>
       </c>
       <c r="AI4">
-        <v>0.365966796875</v>
+        <v>0.02063353676256902</v>
       </c>
       <c r="AJ4">
-        <v>0.0918762088974855</v>
+        <v>-0.0439139814879254</v>
       </c>
       <c r="AK4">
-        <v>0.3050575327803051</v>
+        <v>-0.2303760496531581</v>
       </c>
       <c r="AL4">
-        <v>7.61</v>
+        <v>0.124</v>
       </c>
       <c r="AM4">
-        <v>6.56</v>
+        <v>0.111</v>
       </c>
       <c r="AN4">
-        <v>3.244588744588745</v>
+        <v>0.1288566243194192</v>
       </c>
       <c r="AO4">
-        <v>4.980289093298292</v>
+        <v>4.314516129032258</v>
       </c>
       <c r="AP4">
-        <v>2.467532467532467</v>
+        <v>-1.14519056261343</v>
       </c>
       <c r="AQ4">
-        <v>5.777439024390243</v>
+        <v>4.81981981981982</v>
       </c>
     </row>
     <row r="5">
@@ -996,121 +990,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.137</v>
+        <v>0.173</v>
       </c>
       <c r="E5">
-        <v>0.142</v>
+        <v>0.208</v>
+      </c>
+      <c r="F5">
+        <v>0.068</v>
       </c>
       <c r="G5">
-        <v>0.3156333851150968</v>
+        <v>0.3108124922234665</v>
       </c>
       <c r="H5">
-        <v>0.3156333851150968</v>
+        <v>0.3108124922234665</v>
       </c>
       <c r="I5">
-        <v>0.262251094478181</v>
+        <v>0.2578076396665422</v>
       </c>
       <c r="J5">
-        <v>0.1889974496210352</v>
+        <v>0.1841100295747552</v>
       </c>
       <c r="K5">
-        <v>107.2</v>
+        <v>118.2</v>
       </c>
       <c r="L5">
-        <v>0.1513910464623641</v>
+        <v>0.1470698021649869</v>
       </c>
       <c r="M5">
-        <v>50.42</v>
+        <v>78.78</v>
       </c>
       <c r="N5">
-        <v>0.01356506766391348</v>
+        <v>0.02047989185535654</v>
       </c>
       <c r="O5">
-        <v>0.4703358208955224</v>
+        <v>0.666497461928934</v>
       </c>
       <c r="P5">
-        <v>46</v>
+        <v>74.3</v>
       </c>
       <c r="Q5">
-        <v>0.0123759046517259</v>
+        <v>0.01931525723347285</v>
       </c>
       <c r="R5">
-        <v>0.4291044776119403</v>
+        <v>0.628595600676819</v>
       </c>
       <c r="S5">
-        <v>4.420000000000002</v>
+        <v>4.480000000000004</v>
       </c>
       <c r="T5">
-        <v>0.08766362554541851</v>
+        <v>0.05686722518405692</v>
       </c>
       <c r="U5">
-        <v>173.3</v>
+        <v>192.8</v>
       </c>
       <c r="V5">
-        <v>0.04662487556834997</v>
+        <v>0.05012088283463749</v>
       </c>
       <c r="W5">
-        <v>0.1386266649424544</v>
+        <v>0.1360497237569061</v>
       </c>
       <c r="X5">
-        <v>0.04702068936514061</v>
+        <v>0.07925391941914689</v>
       </c>
       <c r="Y5">
-        <v>0.09160597557731381</v>
+        <v>0.05679580433775919</v>
       </c>
       <c r="Z5">
-        <v>1.383548261039469</v>
+        <v>1.687027707808564</v>
       </c>
       <c r="AA5">
-        <v>0.2614870927640778</v>
+        <v>0.3105987211780663</v>
       </c>
       <c r="AB5">
-        <v>0.04280393857006738</v>
+        <v>0.07261190604865525</v>
       </c>
       <c r="AC5">
-        <v>0.2186831541940105</v>
+        <v>0.237986815129411</v>
       </c>
       <c r="AD5">
-        <v>592.3</v>
+        <v>646.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>592.3</v>
+        <v>646.8</v>
       </c>
       <c r="AG5">
-        <v>418.9999999999999</v>
+        <v>453.9999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.1374501067483524</v>
+        <v>0.1439412484700122</v>
       </c>
       <c r="AI5">
-        <v>0.3840617299961095</v>
+        <v>0.3410313192027839</v>
       </c>
       <c r="AJ5">
-        <v>0.1013080587054813</v>
+        <v>0.1055642104773641</v>
       </c>
       <c r="AK5">
-        <v>0.3060851778800497</v>
+        <v>0.2664631999060922</v>
       </c>
       <c r="AL5">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
       <c r="AM5">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
       <c r="AN5">
-        <v>2.650111856823266</v>
+        <v>2.589271417133707</v>
       </c>
       <c r="AO5">
-        <v>17.5188679245283</v>
+        <v>16.70967741935484</v>
       </c>
       <c r="AP5">
-        <v>1.874720357941834</v>
+        <v>1.817453963170536</v>
       </c>
       <c r="AQ5">
-        <v>17.5188679245283</v>
+        <v>16.70967741935484</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ensurance Limited (ASX:ENA)</t>
+          <t>PSC Insurance Group Limited (ASX:PSI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1130,115 +1127,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0741</v>
+        <v>0.262</v>
+      </c>
+      <c r="E6">
+        <v>0.0621</v>
       </c>
       <c r="G6">
-        <v>-0.08558282208588959</v>
+        <v>0.3703917050691244</v>
       </c>
       <c r="H6">
-        <v>-0.08558282208588959</v>
+        <v>0.3703917050691244</v>
       </c>
       <c r="I6">
-        <v>-0.09110429447852761</v>
+        <v>0.3122119815668203</v>
       </c>
       <c r="J6">
-        <v>-0.09110429447852761</v>
+        <v>0.1928368121442125</v>
       </c>
       <c r="K6">
-        <v>-0.977</v>
+        <v>18.4</v>
       </c>
       <c r="L6">
-        <v>-0.2996932515337423</v>
+        <v>0.1059907834101382</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>24.4</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.020233850236338</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.326086956521739</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>24.4</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.020233850236338</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.326086956521739</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>1.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="V6">
-        <v>0.07857142857142858</v>
+        <v>0.06061862509329131</v>
       </c>
       <c r="W6">
-        <v>1.329251700680272</v>
+        <v>0.07106991116261105</v>
       </c>
       <c r="X6">
-        <v>0.04746445115939574</v>
+        <v>0.07803818783041784</v>
       </c>
       <c r="Y6">
-        <v>1.281787249520876</v>
+        <v>-0.006968276667806791</v>
       </c>
       <c r="Z6">
-        <v>1.817168338907469</v>
+        <v>1.411382113821138</v>
       </c>
       <c r="AA6">
-        <v>-0.1655518394648829</v>
+        <v>0.2721664275466285</v>
       </c>
       <c r="AB6">
-        <v>0.04350902456057459</v>
+        <v>0.07321875163214457</v>
       </c>
       <c r="AC6">
-        <v>-0.2090608640254575</v>
+        <v>0.1989476759144839</v>
       </c>
       <c r="AD6">
-        <v>2.54</v>
+        <v>144.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.54</v>
+        <v>144.9</v>
       </c>
       <c r="AG6">
-        <v>1.44</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.1535671100362757</v>
+        <v>0.1072697660645543</v>
       </c>
       <c r="AI6">
-        <v>0.9463487332339791</v>
+        <v>0.3397420867526378</v>
       </c>
       <c r="AJ6">
-        <v>0.09326424870466321</v>
+        <v>0.05619472489629804</v>
       </c>
       <c r="AK6">
-        <v>0.9090909090909092</v>
+        <v>0.2031692133559706</v>
       </c>
       <c r="AL6">
-        <v>0.497</v>
+        <v>6.5</v>
       </c>
       <c r="AM6">
-        <v>0.497</v>
+        <v>5.967</v>
       </c>
       <c r="AN6">
-        <v>-9.103942652329748</v>
+        <v>2.253499222395023</v>
       </c>
       <c r="AO6">
-        <v>-0.5975855130784709</v>
+        <v>8.338461538461539</v>
       </c>
       <c r="AP6">
-        <v>-5.161290322580644</v>
+        <v>1.116640746500778</v>
       </c>
       <c r="AQ6">
-        <v>-0.5975855130784709</v>
+        <v>9.083291436232614</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2175</v>
+        <v>0.243</v>
       </c>
       <c r="E2">
-        <v>0.196</v>
+        <v>0.151</v>
       </c>
       <c r="F2">
-        <v>0.08449999999999999</v>
+        <v>0.09975000000000001</v>
       </c>
       <c r="G2">
-        <v>0.3109295174450982</v>
+        <v>0.2963739014027122</v>
       </c>
       <c r="H2">
-        <v>0.3109295174450982</v>
+        <v>0.2963739014027122</v>
       </c>
       <c r="I2">
-        <v>0.5796859584597266</v>
+        <v>0.2452987070593059</v>
       </c>
       <c r="J2">
-        <v>0.4563413092709121</v>
+        <v>0.1720210711631391</v>
       </c>
       <c r="K2">
-        <v>192.489</v>
+        <v>206.4</v>
       </c>
       <c r="L2">
-        <v>0.1553545918985013</v>
+        <v>0.1201327047319714</v>
       </c>
       <c r="M2">
-        <v>131.88</v>
+        <v>154.79</v>
       </c>
       <c r="N2">
-        <v>0.01991453120517041</v>
+        <v>0.02040146562631801</v>
       </c>
       <c r="O2">
-        <v>0.6851300593800165</v>
+        <v>0.7499515503875969</v>
       </c>
       <c r="P2">
-        <v>127.4</v>
+        <v>151.2</v>
       </c>
       <c r="Q2">
-        <v>0.01923802908355103</v>
+        <v>0.01992830029523408</v>
       </c>
       <c r="R2">
-        <v>0.6618560021611624</v>
+        <v>0.7325581395348837</v>
       </c>
       <c r="S2">
-        <v>4.480000000000004</v>
+        <v>3.590000000000003</v>
       </c>
       <c r="T2">
-        <v>0.0339702760084926</v>
+        <v>0.02319271270753927</v>
       </c>
       <c r="U2">
-        <v>445.302</v>
+        <v>393.3</v>
       </c>
       <c r="V2">
-        <v>0.06724280083958746</v>
+        <v>0.05183730493462674</v>
       </c>
       <c r="W2">
-        <v>0.1456230786519276</v>
+        <v>0.1084783732552128</v>
       </c>
       <c r="X2">
-        <v>0.07864605362478236</v>
+        <v>0.07059617616882534</v>
       </c>
       <c r="Y2">
-        <v>0.0669770250271452</v>
+        <v>0.0378821970863875</v>
       </c>
       <c r="Z2">
-        <v>1.004224664835961</v>
+        <v>2.239569235593687</v>
       </c>
       <c r="AA2">
-        <v>0.3241756232152957</v>
+        <v>0.3417022991137596</v>
       </c>
       <c r="AB2">
-        <v>0.07291532884039992</v>
+        <v>0.06527252399920312</v>
       </c>
       <c r="AC2">
-        <v>0.2503927532758544</v>
+        <v>0.2761570953394913</v>
       </c>
       <c r="AD2">
-        <v>843.271</v>
+        <v>1287.3</v>
       </c>
       <c r="AE2">
-        <v>464.9335344482246</v>
+        <v>0.05645700703224652</v>
       </c>
       <c r="AF2">
-        <v>1308.204534448225</v>
+        <v>1287.356457007032</v>
       </c>
       <c r="AG2">
-        <v>862.9025344482246</v>
+        <v>894.0564570070323</v>
       </c>
       <c r="AH2">
-        <v>0.1649585507158713</v>
+        <v>0.1450614983682459</v>
       </c>
       <c r="AI2">
-        <v>0.3705568691602543</v>
+        <v>0.3146065874680982</v>
       </c>
       <c r="AJ2">
-        <v>0.1152811203807772</v>
+        <v>0.1054155668489876</v>
       </c>
       <c r="AK2">
-        <v>0.2797025109824711</v>
+        <v>0.2417246552631997</v>
       </c>
       <c r="AL2">
-        <v>23.674</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="AM2">
-        <v>23.128</v>
+        <v>70.50999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.9669973430453036</v>
+        <v>2.527790377784192</v>
       </c>
       <c r="AO2">
-        <v>13.70427473177325</v>
+        <v>5.59256801592568</v>
       </c>
       <c r="AP2">
-        <v>0.9895092539865498</v>
+        <v>1.755602663884256</v>
       </c>
       <c r="AQ2">
-        <v>14.02780179868558</v>
+        <v>5.976457240107787</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0709</v>
+        <v>0.243</v>
       </c>
       <c r="E3">
-        <v>0.196</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F3">
-        <v>0.101</v>
+        <v>0.0915</v>
       </c>
       <c r="G3">
-        <v>0.2750292169848071</v>
+        <v>0.2509533321227528</v>
       </c>
       <c r="H3">
-        <v>0.2750292169848071</v>
+        <v>0.2509533321227528</v>
       </c>
       <c r="I3">
-        <v>1.777613140281866</v>
+        <v>0.2031009780254104</v>
       </c>
       <c r="J3">
-        <v>1.452491497047416</v>
+        <v>0.1464439676069745</v>
       </c>
       <c r="K3">
-        <v>55.7</v>
+        <v>43.4</v>
       </c>
       <c r="L3">
-        <v>0.2169848071679003</v>
+        <v>0.07880878881423642</v>
       </c>
       <c r="M3">
-        <v>28.7</v>
+        <v>34.9</v>
       </c>
       <c r="N3">
-        <v>0.01846015308419631</v>
+        <v>0.01701940895347703</v>
       </c>
       <c r="O3">
-        <v>0.5152603231597845</v>
+        <v>0.804147465437788</v>
       </c>
       <c r="P3">
-        <v>28.7</v>
+        <v>34.9</v>
       </c>
       <c r="Q3">
-        <v>0.01846015308419631</v>
+        <v>0.01701940895347703</v>
       </c>
       <c r="R3">
-        <v>0.5152603231597845</v>
+        <v>0.804147465437788</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>178.7</v>
+        <v>173.3</v>
       </c>
       <c r="V3">
-        <v>0.1149417894127484</v>
+        <v>0.08451185019018825</v>
       </c>
       <c r="W3">
-        <v>0.155196433546949</v>
+        <v>0.07372175980975029</v>
       </c>
       <c r="X3">
-        <v>0.08340977515835937</v>
+        <v>0.07173517036277739</v>
       </c>
       <c r="Y3">
-        <v>0.07178665838858966</v>
+        <v>0.0019865894469729</v>
       </c>
       <c r="Z3">
-        <v>0.4056358995321256</v>
+        <v>7.259764319719639</v>
       </c>
       <c r="AA3">
-        <v>0.5891826949675923</v>
+        <v>1.063148690871292</v>
       </c>
       <c r="AB3">
-        <v>0.07086761395294827</v>
+        <v>0.0646316211086089</v>
       </c>
       <c r="AC3">
-        <v>0.5183150810146441</v>
+        <v>0.9985170697626828</v>
       </c>
       <c r="AD3">
-        <v>51.5</v>
+        <v>440</v>
       </c>
       <c r="AE3">
-        <v>464.9335344482246</v>
+        <v>0.05645700703224652</v>
       </c>
       <c r="AF3">
-        <v>516.4335344482247</v>
+        <v>440.0564570070322</v>
       </c>
       <c r="AG3">
-        <v>337.7335344482247</v>
+        <v>266.7564570070322</v>
       </c>
       <c r="AH3">
-        <v>0.2493482558505378</v>
+        <v>0.1766829205886702</v>
       </c>
       <c r="AI3">
-        <v>0.4289908194698457</v>
+        <v>0.3040625280173782</v>
       </c>
       <c r="AJ3">
-        <v>0.1784652027669217</v>
+        <v>0.1151123972319563</v>
       </c>
       <c r="AK3">
-        <v>0.3294532108248793</v>
+        <v>0.2093921307434134</v>
       </c>
       <c r="AL3">
-        <v>4.65</v>
+        <v>48</v>
       </c>
       <c r="AM3">
-        <v>4.65</v>
+        <v>48</v>
       </c>
       <c r="AN3">
-        <v>0.09239325439540726</v>
+        <v>3.18243297000557</v>
       </c>
       <c r="AO3">
-        <v>13.44086021505376</v>
+        <v>2.329166666666667</v>
       </c>
       <c r="AP3">
-        <v>0.6059087449734925</v>
+        <v>1.929396690320574</v>
       </c>
       <c r="AQ3">
-        <v>13.44086021505376</v>
+        <v>2.329166666666667</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ensurance Limited (ASX:ENA)</t>
+          <t>PSC Insurance Group Limited (ASX:PSI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,115 +862,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.486</v>
+        <v>0.247</v>
+      </c>
+      <c r="E4">
+        <v>0.151</v>
       </c>
       <c r="G4">
-        <v>0.1095427435387674</v>
+        <v>0.3228142783238489</v>
       </c>
       <c r="H4">
-        <v>0.1095427435387674</v>
+        <v>0.3228142783238489</v>
       </c>
       <c r="I4">
-        <v>0.1063618290258449</v>
+        <v>0.2648732540093119</v>
       </c>
       <c r="J4">
-        <v>0.1063618290258449</v>
+        <v>0.1875562024623377</v>
       </c>
       <c r="K4">
-        <v>0.189</v>
+        <v>37.1</v>
       </c>
       <c r="L4">
-        <v>0.03757455268389662</v>
+        <v>0.1919296430419038</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>28.8</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02481261307831481</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.7762803234501348</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>28.8</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02481261307831481</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.7762803234501348</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.702</v>
+        <v>47.5</v>
       </c>
       <c r="V4">
-        <v>0.04679999999999999</v>
+        <v>0.04092358059791505</v>
       </c>
       <c r="W4">
-        <v>1.3125</v>
+        <v>0.1323109843081313</v>
       </c>
       <c r="X4">
-        <v>0.07511379131035709</v>
+        <v>0.07014326510121122</v>
       </c>
       <c r="Y4">
-        <v>1.237386208689643</v>
+        <v>0.06216771920692005</v>
       </c>
       <c r="Z4">
-        <v>3.175505050505051</v>
+        <v>1.821866163996231</v>
       </c>
       <c r="AA4">
-        <v>0.3377525252525252</v>
+        <v>0.3417022991137596</v>
       </c>
       <c r="AB4">
-        <v>0.07495383383022734</v>
+        <v>0.06554520377426826</v>
       </c>
       <c r="AC4">
-        <v>0.2627986914222979</v>
+        <v>0.2761570953394913</v>
       </c>
       <c r="AD4">
-        <v>0.07099999999999999</v>
+        <v>156.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.07099999999999999</v>
+        <v>156.9</v>
       </c>
       <c r="AG4">
-        <v>-0.631</v>
+        <v>109.4</v>
       </c>
       <c r="AH4">
-        <v>0.004711034436998208</v>
+        <v>0.11908014571949</v>
       </c>
       <c r="AI4">
-        <v>0.02063353676256902</v>
+        <v>0.3409387222946545</v>
       </c>
       <c r="AJ4">
-        <v>-0.0439139814879254</v>
+        <v>0.0861349500039367</v>
       </c>
       <c r="AK4">
-        <v>-0.2303760496531581</v>
+        <v>0.2650835958323237</v>
       </c>
       <c r="AL4">
-        <v>0.124</v>
+        <v>6.75</v>
       </c>
       <c r="AM4">
-        <v>0.111</v>
+        <v>1.91</v>
       </c>
       <c r="AN4">
-        <v>0.1288566243194192</v>
+        <v>2.514423076923077</v>
       </c>
       <c r="AO4">
-        <v>4.314516129032258</v>
+        <v>7.585185185185185</v>
       </c>
       <c r="AP4">
-        <v>-1.14519056261343</v>
+        <v>1.753205128205128</v>
       </c>
       <c r="AQ4">
-        <v>4.81981981981982</v>
+        <v>26.80628272251309</v>
       </c>
     </row>
     <row r="5">
@@ -990,258 +996,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.173</v>
+        <v>0.195</v>
       </c>
       <c r="E5">
-        <v>0.208</v>
+        <v>0.201</v>
       </c>
       <c r="F5">
-        <v>0.068</v>
+        <v>0.108</v>
       </c>
       <c r="G5">
-        <v>0.3108124922234665</v>
+        <v>0.3168052561338672</v>
       </c>
       <c r="H5">
-        <v>0.3108124922234665</v>
+        <v>0.3168052561338672</v>
       </c>
       <c r="I5">
-        <v>0.2578076396665422</v>
+        <v>0.2652705061082024</v>
       </c>
       <c r="J5">
-        <v>0.1841100295747552</v>
+        <v>0.1789720014508388</v>
       </c>
       <c r="K5">
-        <v>118.2</v>
+        <v>125.9</v>
       </c>
       <c r="L5">
-        <v>0.1470698021649869</v>
+        <v>0.1292475105225336</v>
       </c>
       <c r="M5">
-        <v>78.78</v>
+        <v>91.09</v>
       </c>
       <c r="N5">
-        <v>0.02047989185535654</v>
+        <v>0.02081628922050321</v>
       </c>
       <c r="O5">
-        <v>0.666497461928934</v>
+        <v>0.7235107227958697</v>
       </c>
       <c r="P5">
-        <v>74.3</v>
+        <v>87.5</v>
       </c>
       <c r="Q5">
-        <v>0.01931525723347285</v>
+        <v>0.01999588656047899</v>
       </c>
       <c r="R5">
-        <v>0.628595600676819</v>
+        <v>0.6949960285941222</v>
       </c>
       <c r="S5">
-        <v>4.480000000000004</v>
+        <v>3.590000000000003</v>
       </c>
       <c r="T5">
-        <v>0.05686722518405692</v>
+        <v>0.03941157097376225</v>
       </c>
       <c r="U5">
-        <v>192.8</v>
+        <v>172.5</v>
       </c>
       <c r="V5">
-        <v>0.05012088283463749</v>
+        <v>0.03942046207637286</v>
       </c>
       <c r="W5">
-        <v>0.1360497237569061</v>
+        <v>0.1084783732552128</v>
       </c>
       <c r="X5">
-        <v>0.07925391941914689</v>
+        <v>0.07059617616882534</v>
       </c>
       <c r="Y5">
-        <v>0.05679580433775919</v>
+        <v>0.0378821970863875</v>
       </c>
       <c r="Z5">
-        <v>1.687027707808564</v>
+        <v>1.664559125085441</v>
       </c>
       <c r="AA5">
-        <v>0.3105987211780663</v>
+        <v>0.2979094781497986</v>
       </c>
       <c r="AB5">
-        <v>0.07261190604865525</v>
+        <v>0.06527252399920312</v>
       </c>
       <c r="AC5">
-        <v>0.237986815129411</v>
+        <v>0.2326369541505955</v>
       </c>
       <c r="AD5">
-        <v>646.8</v>
+        <v>690.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>646.8</v>
+        <v>690.4</v>
       </c>
       <c r="AG5">
-        <v>453.9999999999999</v>
+        <v>517.9</v>
       </c>
       <c r="AH5">
-        <v>0.1439412484700122</v>
+        <v>0.1362730197580088</v>
       </c>
       <c r="AI5">
-        <v>0.3410313192027839</v>
+        <v>0.3160448615243763</v>
       </c>
       <c r="AJ5">
-        <v>0.1055642104773641</v>
+        <v>0.1058277820916261</v>
       </c>
       <c r="AK5">
-        <v>0.2664631999060922</v>
+        <v>0.2574055666003976</v>
       </c>
       <c r="AL5">
-        <v>12.4</v>
+        <v>20.6</v>
       </c>
       <c r="AM5">
-        <v>12.4</v>
+        <v>20.6</v>
       </c>
       <c r="AN5">
-        <v>2.589271417133707</v>
+        <v>2.237200259235256</v>
       </c>
       <c r="AO5">
-        <v>16.70967741935484</v>
+        <v>12.54368932038835</v>
       </c>
       <c r="AP5">
-        <v>1.817453963170536</v>
+        <v>1.678224238496435</v>
       </c>
       <c r="AQ5">
-        <v>16.70967741935484</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PSC Insurance Group Limited (ASX:PSI)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.262</v>
-      </c>
-      <c r="E6">
-        <v>0.0621</v>
-      </c>
-      <c r="G6">
-        <v>0.3703917050691244</v>
-      </c>
-      <c r="H6">
-        <v>0.3703917050691244</v>
-      </c>
-      <c r="I6">
-        <v>0.3122119815668203</v>
-      </c>
-      <c r="J6">
-        <v>0.1928368121442125</v>
-      </c>
-      <c r="K6">
-        <v>18.4</v>
-      </c>
-      <c r="L6">
-        <v>0.1059907834101382</v>
-      </c>
-      <c r="M6">
-        <v>24.4</v>
-      </c>
-      <c r="N6">
-        <v>0.020233850236338</v>
-      </c>
-      <c r="O6">
-        <v>1.326086956521739</v>
-      </c>
-      <c r="P6">
-        <v>24.4</v>
-      </c>
-      <c r="Q6">
-        <v>0.020233850236338</v>
-      </c>
-      <c r="R6">
-        <v>1.326086956521739</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="V6">
-        <v>0.06061862509329131</v>
-      </c>
-      <c r="W6">
-        <v>0.07106991116261105</v>
-      </c>
-      <c r="X6">
-        <v>0.07803818783041784</v>
-      </c>
-      <c r="Y6">
-        <v>-0.006968276667806791</v>
-      </c>
-      <c r="Z6">
-        <v>1.411382113821138</v>
-      </c>
-      <c r="AA6">
-        <v>0.2721664275466285</v>
-      </c>
-      <c r="AB6">
-        <v>0.07321875163214457</v>
-      </c>
-      <c r="AC6">
-        <v>0.1989476759144839</v>
-      </c>
-      <c r="AD6">
-        <v>144.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>144.9</v>
-      </c>
-      <c r="AG6">
-        <v>71.80000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.1072697660645543</v>
-      </c>
-      <c r="AI6">
-        <v>0.3397420867526378</v>
-      </c>
-      <c r="AJ6">
-        <v>0.05619472489629804</v>
-      </c>
-      <c r="AK6">
-        <v>0.2031692133559706</v>
-      </c>
-      <c r="AL6">
-        <v>6.5</v>
-      </c>
-      <c r="AM6">
-        <v>5.967</v>
-      </c>
-      <c r="AN6">
-        <v>2.253499222395023</v>
-      </c>
-      <c r="AO6">
-        <v>8.338461538461539</v>
-      </c>
-      <c r="AP6">
-        <v>1.116640746500778</v>
-      </c>
-      <c r="AQ6">
-        <v>9.083291436232614</v>
+        <v>12.54368932038835</v>
       </c>
     </row>
   </sheetData>
